--- a/data/gravel/Bianchi Arcadex 2025.xlsx
+++ b/data/gravel/Bianchi Arcadex 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10824"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC6A6517-35E0-D74E-805D-C7438C25E6A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{164796E1-8BA4-F44B-B63F-EA3997736B4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31500" yWindow="-23140" windowWidth="29740" windowHeight="16920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="101">
   <si>
     <t>brand</t>
   </si>
@@ -329,7 +329,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="14"/>
       <color rgb="FF000000"/>
@@ -340,6 +340,11 @@
       <color rgb="FF000000"/>
       <name val="Futura"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color rgb="FFCBC4B8"/>
+      <name val="Roboto"/>
     </font>
   </fonts>
   <fills count="2">
@@ -362,10 +367,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1512,13 +1518,11 @@
         <v>30</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:2" ht="23" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>37</v>
       </c>
-      <c r="B43" s="1" t="s">
-        <v>72</v>
-      </c>
+      <c r="B43" s="3"/>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" t="s">

--- a/data/gravel/Bianchi Arcadex 2025.xlsx
+++ b/data/gravel/Bianchi Arcadex 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{164796E1-8BA4-F44B-B63F-EA3997736B4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C291640B-E21A-4C48-9D2D-0DF5D6AFB56E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="102">
   <si>
     <t>brand</t>
   </si>
@@ -323,6 +323,9 @@
   </si>
   <si>
     <t>a8:g31</t>
+  </si>
+  <si>
+    <t>https://www.bianchi.com/store/media/catalog/product/cache/5d734973a3a57882312a39134da547d8/Y/T/YTB82IAF-1_4.jpg</t>
   </si>
 </sst>
 </file>
@@ -715,6 +718,11 @@
         <v>74</v>
       </c>
     </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>101</v>
+      </c>
+    </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>5</v>

--- a/data/gravel/Bianchi Arcadex 2025.xlsx
+++ b/data/gravel/Bianchi Arcadex 2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C291640B-E21A-4C48-9D2D-0DF5D6AFB56E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{442F20BB-0385-D24E-9995-B20B586CB7D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30440" yWindow="-19600" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="104">
   <si>
     <t>brand</t>
   </si>
@@ -326,6 +326,12 @@
   </si>
   <si>
     <t>https://www.bianchi.com/store/media/catalog/product/cache/5d734973a3a57882312a39134da547d8/Y/T/YTB82IAF-1_4.jpg</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Treviglio, Italy</t>
   </si>
 </sst>
 </file>
@@ -671,7 +677,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X71"/>
+  <dimension ref="A1:X72"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.6640625" customWidth="1"/>
@@ -1724,6 +1730,14 @@
         <v>73</v>
       </c>
     </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>102</v>
+      </c>
+      <c r="B72" t="s">
+        <v>103</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/gravel/Bianchi Arcadex 2025.xlsx
+++ b/data/gravel/Bianchi Arcadex 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{442F20BB-0385-D24E-9995-B20B586CB7D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9971ABF3-317B-AD4E-8B22-436000A06A12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="30440" yWindow="-19600" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="110">
   <si>
     <t>brand</t>
   </si>
@@ -332,6 +332,24 @@
   </si>
   <si>
     <t>Treviglio, Italy</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -677,7 +695,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X72"/>
+  <dimension ref="A1:X78"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.6640625" customWidth="1"/>
@@ -1566,131 +1584,113 @@
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>42</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>43</v>
+        <v>105</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>44</v>
-      </c>
-      <c r="B50">
-        <v>27.2</v>
+        <v>106</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>45</v>
-      </c>
-      <c r="B51" s="1"/>
+        <v>107</v>
+      </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>46</v>
+        <v>108</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>47</v>
+        <v>109</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>48</v>
-      </c>
-      <c r="B54">
-        <v>160</v>
+        <v>42</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>49</v>
-      </c>
-      <c r="B55">
-        <v>160</v>
+        <v>43</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>50</v>
+        <v>44</v>
+      </c>
+      <c r="B56">
+        <v>27.2</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>51</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>99</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="B57" s="1"/>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>54</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>72</v>
+        <v>48</v>
+      </c>
+      <c r="B60">
+        <v>160</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B61">
-        <v>2</v>
+        <v>160</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>56</v>
-      </c>
-      <c r="B62">
-        <v>1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>72</v>
+        <v>99</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>58</v>
-      </c>
-      <c r="B64">
-        <v>3</v>
+        <v>52</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>59</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>72</v>
@@ -1698,43 +1698,91 @@
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>61</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>72</v>
+        <v>55</v>
+      </c>
+      <c r="B67">
+        <v>2</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>62</v>
+        <v>56</v>
+      </c>
+      <c r="B68">
+        <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>63</v>
-      </c>
-      <c r="B69">
-        <v>3500</v>
+        <v>57</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>64</v>
+        <v>58</v>
+      </c>
+      <c r="B70">
+        <v>3</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
+        <v>60</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>61</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>63</v>
+      </c>
+      <c r="B75">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>65</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
         <v>102</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B78" t="s">
         <v>103</v>
       </c>
     </row>
